--- a/00_Project_Management/Research_Progress_Log.xlsx
+++ b/00_Project_Management/Research_Progress_Log.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Screen candidates C001–C010</t>
+          <t>Screen candidates C001–C010 and sync master matrix</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>All ten discovery candidates screened as Include; assigned Final Paper IDs P009–P018; Litmap addition pending</t>
+          <t>All ten discovery candidates marked Added to Litmap=Yes; master Literature_Matrix expanded to P001–P018</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Literature_Review_Matrix.xlsx (Litmaps_Discovery_Screening)</t>
+          <t>Literature_Review_Matrix.xlsx; litmaps_step_2_3_included_papers_tagged_v01.png</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Completed — screening done; addition pending</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1065,7 +1065,133 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Add included candidates to Litmap and create Literature_Matrix rows P009–P018</t>
+          <t>Begin Step 2.4 metadata verification and full-text collection for P001–P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Step 2.3C</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Litmap and master-matrix reconciliation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Identified Rashid et al. (2021) as an additional relevant saved article and assigned C011/P019.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4 metadata verification and full-text collection for P001–P019</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Step 2.4A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P001 metadata verification and full-text extraction</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Verified official metadata; downloaded and reviewed the full text; extracted objective, study area, datasets, preprocessing, Random Forest configuration, accuracy, findings, author-stated limitations, critical gaps, and relevance to the proposed study.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>P001_2018_hassan_extraction_notes.docx; Literature_Review_Matrix_P001_Completed.xlsx; 2018_hassan_rohingya_refugee_crisis_forest_cover_change.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4B: P002 Dampha et al. (2022) metadata verification and full-text extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>13 July 2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Step 2.4B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P002 metadata verification and full-text extraction</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Verified official metadata and extracted datasets, Random Forest classification, treatment-control design, DiD model, robustness tests, findings, limitations and research gap</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P002_2022_dampha_extraction_notes.docx; Literature_Review_Matrix.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Detailed public appendices were unavailable; inconsistent settlement-area reporting was identified</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4C — P003 Hassan et al. (2023)</t>
         </is>
       </c>
     </row>

--- a/00_Project_Management/Research_Progress_Log.xlsx
+++ b/00_Project_Management/Research_Progress_Log.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -1195,6 +1195,468 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Step 2.4D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P004 metadata verification and partial extraction</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Verified official metadata, abstract, objectives, reported periods, machine-learning approaches, principal findings, prediction horizon, relevance, limitations and research gap</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P004_2022_rahaman_partial_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Partially Completed — Full Text Unavailable</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ScienceDirect full text requires paid access; detailed datasets, accuracy assessment and model settings could not be verified</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4E — P005 metadata verification and full-text collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Step 2.4E</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P005 metadata verification and full-text extraction</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Verified official metadata and extracted restoration context, sampling design, biomass-estimation procedures, five carbon pools, allometric models, numerical findings, limitations, relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Research_Papers/03_Biomass_Carbon_Studies/2025_mahmood_tracking_forest_recovery_biomass_carbon.pdf; Paper_Extraction_Notes/P005_2025_mahmood_extraction_notes.docx; Literature_Review_Matrix.xlsx (P005); Literature_Notes.docx (Biomass and Carbon); P005_Extraction sheet</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>None blocking. Noted publisher Highlights AGB/BGB swap vs abstract/Table 6; species-count inconsistency abstract vs Results/Table 3; minor 93.90 vs 93.95 mean C wording.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4F — P006 Mitra et al. (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Step 2.4F</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P006 metadata verification and full-text extraction</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verified official metadata and extracted Sentinel-2 image dates, Random Forest design, training-validation samples, classification accuracy, LULC change, FRAGSTATS metrics, NDVI analysis, camp-level population relationships, restoration signals, limitations, research relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Research_Papers/02_Fragmentation_Studies/2025_mitra_landscape_fragmentation_population_distribution.pdf; Paper_Extraction_Notes/P006_2025_mitra_extraction_notes.docx; Literature_Review_Matrix.xlsx (P006); Literature_Notes.docx (Fragmentation; Population and Drivers); P006_Extraction sheet</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Only two dates were analysed; historical population data were unavailable; settlement change was used as a population proxy; Camp 15 forest-loss reporting differs slightly between the abstract and results text.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4G — P007 Arkhangelsky et al. (2021), Synthetic Difference-in-Differences methodological review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Step 2.4G</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P007 SDID methodological full-text review</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Verified the journal metadata and reviewed the open revised manuscript; extracted panel requirements, unit weights, time weights, weighted fixed-effects estimator, identification logic, theoretical properties, bootstrap, jackknife and placebo inference, application limitations, required diagnostics and relevance to the proposed forest-loss attribution design.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P007_2021_arkhangelsky_sdid_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>The standard formulation uses binary treatment and does not automatically address spatial interference, continuous exposure, classification uncertainty or spatially correlated outcomes.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4H — P008 Salemi (2025) causal land-cover working paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Step 2.4H</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P008 causal land-cover working-paper full-text review</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Verified the latest author-hosted working-paper version and extracted Dynamic World data processing, treatment and spillover zones, propensity-score matching, event-study specification, fixed effects, spatially clustered standard errors, forest and settlement effects, protected-area and Kutupalong heterogeneity, robustness checks, nighttime-light analysis, intervention interpretation, limitations and implications for research novelty.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P008_2025_salemi_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>The paper is under review rather than peer reviewed; only two pre-treatment years are available; LPG and fencing effects cannot be separated; Dynamic World and nighttime-light measurement limitations remain.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4I — P009 Langer et al. (2015) methodological/restoration review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Step 2.4I</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P009 long-term refugee-camp environmental monitoring and restoration full-text review</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Verified metadata and reviewed the open-access short paper; extracted the Lukole camp lifecycle, spatial buffer, Landsat archive, multi-sensor SIAM preprocessing, greenness index, object-based change detection, preliminary deforestation and reforestation findings, methodological advantages, limitations and relevance to long-term recovery analysis.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>P009_2015_langer_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>The paper reports preliminary findings only; no quantitative deforestation/reforestation areas, accuracy assessment or uncertainty analysis are provided. Publisher and institutional records disagree on the volume number.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4J — P010 Hasan et al. (2020) full-text review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Step 2.4J</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P010 forest degradation, ecosystem-function loss and CA–Markov prediction full-text review</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Verified final journal and online-first metadata; reviewed the author-uploaded full text; extracted study area, Sentinel-2A classification, forest-beat coverage, observed degradation, CA–Markov prediction, degradation drivers, biomass and carbon-stock methods, ecosystem-function implications, limitations and relevance to the proposed integrated research design.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>P010_2021_hasan_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Final issue year is 2021 although the paper was accepted and first published online in 2020; predicted 2027 loss is reported as both approximately 5,115 and 5,120 ha due to rounding. Automated binary PDF download from ResearchGate/Authorea was blocked by Cloudflare; full text was reviewed from author-uploaded public full text and an archival working PDF was saved.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4K — P011 Sarkar et al. (2023).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Step 2.4K</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P011 ecological-impact, ecosystem-service and fuzzy-EQ full-text review</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verified metadata and reviewed the open full text; extracted Sentinel and Landsat inputs, WorldView/field reference sampling, ANN/RF/SVM settings and accuracy, LULC change, ESV methodology, sensitivity analysis, ecosystem-service results, fuzzy ecological-quality model, Markov transitions, limitations, inconsistencies, research relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>P011_2023_sarkar_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2023_sarkar_ecological_impact_refugee_crisis.pdf</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>The 2017 baseline coincides with the beginning of the major influx; the two images are seasonally mismatched; abstract and Table 5 contain conflicting raw-material and biodiversity percentages; the water-change narrative conflicts with Table 3.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4L — P012 Sarkar et al. (2022), ecosystem-service-cost review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Step 2.4L</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P012 ecosystem-service-cost full-text review</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Verified final and online-first metadata; extracted ANN-based LULC classification, January 2017/2021 Sentinel dates, sample design, 2017–2021 forest and settlement change, benefit-transfer ESV framework, aggregate and service-specific monetary results, sensitivity analysis, limitations, relationship with P011 and implications for evidence independence.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>P012_2023_sarkar_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2023_sarkar_cost_ecosystem_service_value.pdf</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>P011 and P012 share closely related LULC inputs but report materially different ESV totals and service-specific changes; the papers must not be treated as independent evidence. Automated RG binary PDF download blocked; author public full text reviewed and working archive saved.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4M — P013 Ahmed et al. (2024).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Step 2.4M</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P013 long-term LULC, LST and CA–ANN prediction full-text review</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Verified official metadata and reviewed the author-uploaded full article; extracted study domains, eight Landsat dates, iso-cluster classification, LST processing, CA–ANN/MOLUSCE design, calibration and validation, historical camp-area LULC and LST change, 2028 and 2034 predictions, limitations, methodological inconsistencies, research relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>P013_2024_ahmed_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2024_ahmed_rohingya_lulc_lst_machine_learning.pdf</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Historical and predictive analyses use different spatial domains; the broad vegetation class is not forest-specific; only the 2022 LULC map received a reported accuracy assessment; the NDVI–LST R² value is described as a correlation coefficient; CA–ANN hyperparameters and uncertainty are incompletely reported. Binary author PDF download blocked — working archive saved.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4N — P014 Gromny et al. (2024) comparative remote-sensing methodological review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step 2.4N</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P014 annual multi-sensor refugee-camp lifecycle and socioeconomic-driver full-text review</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Verified metadata and reviewed the open-access full text; extracted the Mtendeli camp lifecycle, 40 × 40 km analysis area, distance buffers, WorldCover-derived training data, Sentinel-1, Sentinel-2 and Landsat processing, Random Forest annual mapping, validation design, land-cover transitions, distance-decay pattern, cropland and fuelwood drivers, qualitative interviews, camp-closure effects, restoration findings, limitations and relevance to the proposed Cox’s Bazar analysis.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P014_2024_gromny_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2024_gromny_mtendeli_land_cover_drivers.pdf</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>The time series lacks a clean long pre-camp baseline; only the 2020 annual map and July 2022 single-image classification have reported independent accuracy assessments; the legend changes in 2022; vegetation classes show confusion; qualitative driver evidence is not causal attribution. Automated OA/RG binary PDF download blocked — working archive saved.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4O — P015 Mohiuddin et al. (2025), elephant-route and land-cover conservation review.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/00_Project_Management/Research_Progress_Log.xlsx
+++ b/00_Project_Management/Research_Progress_Log.xlsx
@@ -41,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,11 +49,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -63,6 +77,9 @@
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -1196,44 +1213,44 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>16 July 2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Step 2.4D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>P004 metadata verification and partial extraction</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Verified official metadata, abstract, objectives, reported periods, machine-learning approaches, principal findings, prediction horizon, relevance, limitations and research gap</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>P004_2022_rahaman_partial_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.4C</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>P003 metadata verification and partial review</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Verified metadata, abstract, publisher highlights and accessible section snippets. Recorded P003 as a partial review; complete full text was unavailable, so detailed methods, validation and findings remain conditional.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx; Literature_Notes.docx</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Partially Completed — Full Text Unavailable</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ScienceDirect full text requires paid access; detailed datasets, accuracy assessment and model settings could not be verified</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Begin Step 2.4E — P005 metadata verification and full-text collection</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Complete full text unavailable; only abstract, highlights and accessible section snippets could be verified.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4D — P004 metadata verification and partial extraction</t>
         </is>
       </c>
     </row>
@@ -1245,37 +1262,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Step 2.4E</t>
+          <t>Step 2.4D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P005 metadata verification and full-text extraction</t>
+          <t>P004 metadata verification and partial extraction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Verified official metadata and extracted restoration context, sampling design, biomass-estimation procedures, five carbon pools, allometric models, numerical findings, limitations, relevance and research gap.</t>
+          <t>Verified official metadata, abstract, objectives, reported periods, machine-learning approaches, principal findings, prediction horizon, relevance, limitations and research gap</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Research_Papers/03_Biomass_Carbon_Studies/2025_mahmood_tracking_forest_recovery_biomass_carbon.pdf; Paper_Extraction_Notes/P005_2025_mahmood_extraction_notes.docx; Literature_Review_Matrix.xlsx (P005); Literature_Notes.docx (Biomass and Carbon); P005_Extraction sheet</t>
+          <t>P004_2022_rahaman_partial_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Partially Completed — Full Text Unavailable</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>None blocking. Noted publisher Highlights AGB/BGB swap vs abstract/Table 6; species-count inconsistency abstract vs Results/Table 3; minor 93.90 vs 93.95 mean C wording.</t>
+          <t>ScienceDirect full text requires paid access; detailed datasets, accuracy assessment and model settings could not be verified</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Begin Step 2.4F — P006 Mitra et al. (2025)</t>
+          <t>Begin Step 2.4E — P005 metadata verification and full-text collection</t>
         </is>
       </c>
     </row>
@@ -1287,22 +1304,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Step 2.4F</t>
+          <t>Step 2.4E</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P006 metadata verification and full-text extraction</t>
+          <t>P005 metadata verification and full-text extraction</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Verified official metadata and extracted Sentinel-2 image dates, Random Forest design, training-validation samples, classification accuracy, LULC change, FRAGSTATS metrics, NDVI analysis, camp-level population relationships, restoration signals, limitations, research relevance and research gap.</t>
+          <t>Verified official metadata and extracted restoration context, sampling design, biomass-estimation procedures, five carbon pools, allometric models, numerical findings, limitations, relevance and research gap.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Research_Papers/02_Fragmentation_Studies/2025_mitra_landscape_fragmentation_population_distribution.pdf; Paper_Extraction_Notes/P006_2025_mitra_extraction_notes.docx; Literature_Review_Matrix.xlsx (P006); Literature_Notes.docx (Fragmentation; Population and Drivers); P006_Extraction sheet</t>
+          <t>Research_Papers/03_Biomass_Carbon_Studies/2025_mahmood_tracking_forest_recovery_biomass_carbon.pdf; Paper_Extraction_Notes/P005_2025_mahmood_extraction_notes.docx; Literature_Review_Matrix.xlsx (P005); Literature_Notes.docx (Biomass and Carbon); P005_Extraction sheet</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1312,12 +1329,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Only two dates were analysed; historical population data were unavailable; settlement change was used as a population proxy; Camp 15 forest-loss reporting differs slightly between the abstract and results text.</t>
+          <t>None blocking. Noted publisher Highlights AGB/BGB swap vs abstract/Table 6; species-count inconsistency abstract vs Results/Table 3; minor 93.90 vs 93.95 mean C wording.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Begin Step 2.4G — P007 Arkhangelsky et al. (2021), Synthetic Difference-in-Differences methodological review.</t>
+          <t>Begin Step 2.4F — P006 Mitra et al. (2025)</t>
         </is>
       </c>
     </row>
@@ -1329,22 +1346,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Step 2.4G</t>
+          <t>Step 2.4F</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P007 SDID methodological full-text review</t>
+          <t>P006 metadata verification and full-text extraction</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Verified the journal metadata and reviewed the open revised manuscript; extracted panel requirements, unit weights, time weights, weighted fixed-effects estimator, identification logic, theoretical properties, bootstrap, jackknife and placebo inference, application limitations, required diagnostics and relevance to the proposed forest-loss attribution design.</t>
+          <t>Verified official metadata and extracted Sentinel-2 image dates, Random Forest design, training-validation samples, classification accuracy, LULC change, FRAGSTATS metrics, NDVI analysis, camp-level population relationships, restoration signals, limitations, research relevance and research gap.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P007_2021_arkhangelsky_sdid_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+          <t>Research_Papers/02_Fragmentation_Studies/2025_mitra_landscape_fragmentation_population_distribution.pdf; Paper_Extraction_Notes/P006_2025_mitra_extraction_notes.docx; Literature_Review_Matrix.xlsx (P006); Literature_Notes.docx (Fragmentation; Population and Drivers); P006_Extraction sheet</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1354,12 +1371,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>The standard formulation uses binary treatment and does not automatically address spatial interference, continuous exposure, classification uncertainty or spatially correlated outcomes.</t>
+          <t>Only two dates were analysed; historical population data were unavailable; settlement change was used as a population proxy; Camp 15 forest-loss reporting differs slightly between the abstract and results text.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Begin Step 2.4H — P008 Salemi (2025) causal land-cover working paper.</t>
+          <t>Begin Step 2.4G — P007 Arkhangelsky et al. (2021), Synthetic Difference-in-Differences methodological review.</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1388,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Step 2.4H</t>
+          <t>Step 2.4G</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P008 causal land-cover working-paper full-text review</t>
+          <t>P007 SDID methodological full-text review</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Verified the latest author-hosted working-paper version and extracted Dynamic World data processing, treatment and spillover zones, propensity-score matching, event-study specification, fixed effects, spatially clustered standard errors, forest and settlement effects, protected-area and Kutupalong heterogeneity, robustness checks, nighttime-light analysis, intervention interpretation, limitations and implications for research novelty.</t>
+          <t>Verified the journal metadata and reviewed the open revised manuscript; extracted panel requirements, unit weights, time weights, weighted fixed-effects estimator, identification logic, theoretical properties, bootstrap, jackknife and placebo inference, application limitations, required diagnostics and relevance to the proposed forest-loss attribution design.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P008_2025_salemi_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+          <t>P007_2021_arkhangelsky_sdid_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1396,12 +1413,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The paper is under review rather than peer reviewed; only two pre-treatment years are available; LPG and fencing effects cannot be separated; Dynamic World and nighttime-light measurement limitations remain.</t>
+          <t>The standard formulation uses binary treatment and does not automatically address spatial interference, continuous exposure, classification uncertainty or spatially correlated outcomes.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Begin Step 2.4I — P009 Langer et al. (2015) methodological/restoration review.</t>
+          <t>Begin Step 2.4H — P008 Salemi (2025) causal land-cover working paper.</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1430,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Step 2.4I</t>
+          <t>Step 2.4H</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P009 long-term refugee-camp environmental monitoring and restoration full-text review</t>
+          <t>P008 causal land-cover working-paper full-text review</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Verified metadata and reviewed the open-access short paper; extracted the Lukole camp lifecycle, spatial buffer, Landsat archive, multi-sensor SIAM preprocessing, greenness index, object-based change detection, preliminary deforestation and reforestation findings, methodological advantages, limitations and relevance to long-term recovery analysis.</t>
+          <t>Verified the latest author-hosted working-paper version and extracted Dynamic World data processing, treatment and spillover zones, propensity-score matching, event-study specification, fixed effects, spatially clustered standard errors, forest and settlement effects, protected-area and Kutupalong heterogeneity, robustness checks, nighttime-light analysis, intervention interpretation, limitations and implications for research novelty.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P009_2015_langer_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+          <t>P008_2025_salemi_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1438,12 +1455,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The paper reports preliminary findings only; no quantitative deforestation/reforestation areas, accuracy assessment or uncertainty analysis are provided. Publisher and institutional records disagree on the volume number.</t>
+          <t>The paper is under review rather than peer reviewed; only two pre-treatment years are available; LPG and fencing effects cannot be separated; Dynamic World and nighttime-light measurement limitations remain.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Begin Step 2.4J — P010 Hasan et al. (2020) full-text review.</t>
+          <t>Begin Step 2.4I — P009 Langer et al. (2015) methodological/restoration review.</t>
         </is>
       </c>
     </row>
@@ -1455,22 +1472,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Step 2.4J</t>
+          <t>Step 2.4I</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P010 forest degradation, ecosystem-function loss and CA–Markov prediction full-text review</t>
+          <t>P009 long-term refugee-camp environmental monitoring and restoration full-text review</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Verified final journal and online-first metadata; reviewed the author-uploaded full text; extracted study area, Sentinel-2A classification, forest-beat coverage, observed degradation, CA–Markov prediction, degradation drivers, biomass and carbon-stock methods, ecosystem-function implications, limitations and relevance to the proposed integrated research design.</t>
+          <t>Verified metadata and reviewed the open-access short paper; extracted the Lukole camp lifecycle, spatial buffer, Landsat archive, multi-sensor SIAM preprocessing, greenness index, object-based change detection, preliminary deforestation and reforestation findings, methodological advantages, limitations and relevance to long-term recovery analysis.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P010_2021_hasan_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
+          <t>P009_2015_langer_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1480,12 +1497,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Final issue year is 2021 although the paper was accepted and first published online in 2020; predicted 2027 loss is reported as both approximately 5,115 and 5,120 ha due to rounding. Automated binary PDF download from ResearchGate/Authorea was blocked by Cloudflare; full text was reviewed from author-uploaded public full text and an archival working PDF was saved.</t>
+          <t>The paper reports preliminary findings only; no quantitative deforestation/reforestation areas, accuracy assessment or uncertainty analysis are provided. Publisher and institutional records disagree on the volume number.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Begin Step 2.4K — P011 Sarkar et al. (2023).</t>
+          <t>Begin Step 2.4J — P010 Hasan et al. (2020) full-text review.</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1514,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Step 2.4K</t>
+          <t>Step 2.4J</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P011 ecological-impact, ecosystem-service and fuzzy-EQ full-text review</t>
+          <t>P010 forest degradation, ecosystem-function loss and CA–Markov prediction full-text review</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Verified metadata and reviewed the open full text; extracted Sentinel and Landsat inputs, WorldView/field reference sampling, ANN/RF/SVM settings and accuracy, LULC change, ESV methodology, sensitivity analysis, ecosystem-service results, fuzzy ecological-quality model, Markov transitions, limitations, inconsistencies, research relevance and research gap.</t>
+          <t>Verified final journal and online-first metadata; reviewed the author-uploaded full text; extracted study area, Sentinel-2A classification, forest-beat coverage, observed degradation, CA–Markov prediction, degradation drivers, biomass and carbon-stock methods, ecosystem-function implications, limitations and relevance to the proposed integrated research design.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P011_2023_sarkar_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2023_sarkar_ecological_impact_refugee_crisis.pdf</t>
+          <t>P010_2021_hasan_extraction_notes.docx; Literature_Review_Matrix.xlsx; Research_Decision_Log.docx</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1522,12 +1539,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>The 2017 baseline coincides with the beginning of the major influx; the two images are seasonally mismatched; abstract and Table 5 contain conflicting raw-material and biodiversity percentages; the water-change narrative conflicts with Table 3.</t>
+          <t>Final issue year is 2021 although the paper was accepted and first published online in 2020; predicted 2027 loss is reported as both approximately 5,115 and 5,120 ha due to rounding. Automated binary PDF download from ResearchGate/Authorea was blocked by Cloudflare; full text was reviewed from author-uploaded public full text and an archival working PDF was saved.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Begin Step 2.4L — P012 Sarkar et al. (2022), ecosystem-service-cost review.</t>
+          <t>Begin Step 2.4K — P011 Sarkar et al. (2023).</t>
         </is>
       </c>
     </row>
@@ -1539,22 +1556,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Step 2.4L</t>
+          <t>Step 2.4K</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P012 ecosystem-service-cost full-text review</t>
+          <t>P011 ecological-impact, ecosystem-service and fuzzy-EQ full-text review</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Verified final and online-first metadata; extracted ANN-based LULC classification, January 2017/2021 Sentinel dates, sample design, 2017–2021 forest and settlement change, benefit-transfer ESV framework, aggregate and service-specific monetary results, sensitivity analysis, limitations, relationship with P011 and implications for evidence independence.</t>
+          <t>Verified metadata and reviewed the open full text; extracted Sentinel and Landsat inputs, WorldView/field reference sampling, ANN/RF/SVM settings and accuracy, LULC change, ESV methodology, sensitivity analysis, ecosystem-service results, fuzzy ecological-quality model, Markov transitions, limitations, inconsistencies, research relevance and research gap.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P012_2023_sarkar_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2023_sarkar_cost_ecosystem_service_value.pdf</t>
+          <t>P011_2023_sarkar_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2023_sarkar_ecological_impact_refugee_crisis.pdf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1564,12 +1581,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>P011 and P012 share closely related LULC inputs but report materially different ESV totals and service-specific changes; the papers must not be treated as independent evidence. Automated RG binary PDF download blocked; author public full text reviewed and working archive saved.</t>
+          <t>The 2017 baseline coincides with the beginning of the major influx; the two images are seasonally mismatched; abstract and Table 5 contain conflicting raw-material and biodiversity percentages; the water-change narrative conflicts with Table 3.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Begin Step 2.4M — P013 Ahmed et al. (2024).</t>
+          <t>Begin Step 2.4L — P012 Sarkar et al. (2022), ecosystem-service-cost review.</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1598,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Step 2.4M</t>
+          <t>Step 2.4L</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P013 long-term LULC, LST and CA–ANN prediction full-text review</t>
+          <t>P012 ecosystem-service-cost full-text review</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Verified official metadata and reviewed the author-uploaded full article; extracted study domains, eight Landsat dates, iso-cluster classification, LST processing, CA–ANN/MOLUSCE design, calibration and validation, historical camp-area LULC and LST change, 2028 and 2034 predictions, limitations, methodological inconsistencies, research relevance and research gap.</t>
+          <t>Verified final and online-first metadata; extracted ANN-based LULC classification, January 2017/2021 Sentinel dates, sample design, 2017–2021 forest and settlement change, benefit-transfer ESV framework, aggregate and service-specific monetary results, sensitivity analysis, limitations, relationship with P011 and implications for evidence independence.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P013_2024_ahmed_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2024_ahmed_rohingya_lulc_lst_machine_learning.pdf</t>
+          <t>P012_2023_sarkar_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2023_sarkar_cost_ecosystem_service_value.pdf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1606,12 +1623,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Historical and predictive analyses use different spatial domains; the broad vegetation class is not forest-specific; only the 2022 LULC map received a reported accuracy assessment; the NDVI–LST R² value is described as a correlation coefficient; CA–ANN hyperparameters and uncertainty are incompletely reported. Binary author PDF download blocked — working archive saved.</t>
+          <t>P011 and P012 share closely related LULC inputs but report materially different ESV totals and service-specific changes; the papers must not be treated as independent evidence. Automated RG binary PDF download blocked; author public full text reviewed and working archive saved.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Begin Step 2.4N — P014 Gromny et al. (2024) comparative remote-sensing methodological review.</t>
+          <t>Begin Step 2.4M — P013 Ahmed et al. (2024).</t>
         </is>
       </c>
     </row>
@@ -1623,37 +1640,583 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Step 2.4M</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P013 long-term LULC, LST and CA–ANN prediction full-text review</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Verified official metadata and reviewed the author-uploaded full article; extracted study domains, eight Landsat dates, iso-cluster classification, LST processing, CA–ANN/MOLUSCE design, calibration and validation, historical camp-area LULC and LST change, 2028 and 2034 predictions, limitations, methodological inconsistencies, research relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P013_2024_ahmed_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2024_ahmed_rohingya_lulc_lst_machine_learning.pdf</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Historical and predictive analyses use different spatial domains; the broad vegetation class is not forest-specific; only the 2022 LULC map received a reported accuracy assessment; the NDVI–LST R² value is described as a correlation coefficient; CA–ANN hyperparameters and uncertainty are incompletely reported. Binary author PDF download blocked — working archive saved.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4N — P014 Gromny et al. (2024) comparative remote-sensing methodological review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16 July 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Step 2.4N</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>P014 annual multi-sensor refugee-camp lifecycle and socioeconomic-driver full-text review</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Verified metadata and reviewed the open-access full text; extracted the Mtendeli camp lifecycle, 40 × 40 km analysis area, distance buffers, WorldCover-derived training data, Sentinel-1, Sentinel-2 and Landsat processing, Random Forest annual mapping, validation design, land-cover transitions, distance-decay pattern, cropland and fuelwood drivers, qualitative interviews, camp-closure effects, restoration findings, limitations and relevance to the proposed Cox’s Bazar analysis.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>P014_2024_gromny_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2024_gromny_mtendeli_land_cover_drivers.pdf</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>The time series lacks a clean long pre-camp baseline; only the 2020 annual map and July 2022 single-image classification have reported independent accuracy assessments; the legend changes in 2022; vegetation classes show confusion; qualitative driver evidence is not causal attribution. Automated OA/RG binary PDF download blocked — working archive saved.</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Begin Step 2.4O — P015 Mohiuddin et al. (2025), elephant-route and land-cover conservation review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>18 July 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Step 2.4O</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>P015 Rohingya-related LULC and elephant-route partial review</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Verified official metadata and publisher abstract; extracted the 2016–2021 design, GIS software, Palong Khali and Teknaf forest and settlement changes, elephant-route interpretation, conservation relevance, methodological limitations, ambiguous casualty claim and research gap.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>P015_2025_mohiuddin_partial_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Partially Completed — Full Text Unavailable</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>The Springer article requires subscription access. Satellite sensor, image dates, classification method, validation accuracy, complete LULC results and elephant-route analytical procedure could not be independently verified. The abstract contains an ambiguous casualty claim that will not be used without primary-source verification.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4P — P016 Chowdhury et al. (2025), ecological restoration review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>18 July 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Step 2.4P</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>P016 reforestation recovery, resilience and land-use-legacy full-text review</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Verified official metadata and reviewed the open full text; extracted Kutupalong restoration history, Sentinel-2 Random Forest mapping, classification accuracy, land-use legacy selection, 188-plot field inventory, tree composition, topographic variables, EVI recovery/resilience equations, linear mixed models, LULC changes, annual resilience dynamics, species-richness and elevation effects, limitations, policy implications and relevance to the proposed research.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>P016_2025_chowdhury_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2025_chowdhury_land_use_legacy_reforestation_resilience.pdf</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>The study samples only successfully reforested trajectories, has no untreated control, uses three LULC dates and January-only EVI observations, and does not directly measure biomass, carbon, fragmentation, soil recovery or causal restoration effects.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4Q — P017 Liu et al. (2026), protected-area governance and conservation review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18 July 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Step 2.4Q</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>P017 protected-area governance, ecological-threshold and future-scenario full-text review</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Verified official metadata and reviewed the open-access Version of Record; extracted the 2016–2024 LULC design, Landsat/Sentinel processing, field evidence, InVEST 3.18.0 habitat-quality model, NDVI and LST, landscape-pattern analysis (PD/LPI/ED), protected-area boundary gradient (100/300/500/1000/2000 m buffers), the 300–500 m critical transition zone, PLUS v1.4.2 2036 business-as-usual simulation, zoning and regeneration strategy, limitations, research relevance and gap.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>P017_2026_liu_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2026_liu_land_use_governance_protected_areas.pdf</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>The design includes only one pre-influx year and four observed dates; the 300–500 m spatial threshold is diagnostic rather than causal; InVEST and PLUS results depend on parameter assumptions; a single 2024-trained RF (OA 80.2%/κ 0.73) is applied to all years; no carbon accounting, SDID or jointly propagated uncertainty; the cited 54.6% forest / 598.5% settlement figures originate from P006 (Mitra et al.).</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4R — P018 Sobczak-Szelc et al. (2026), background, migration and environmental-governance review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>18 July 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Step 2.4R</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>P018 common-pool-resource, (mal)coping and socio-environmental-governance full-text review</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Verified the final 2026 bibliographic record and reviewed the open-access full text; extracted the integrated socio-ecological framework, common-pool resources, transformative adaptation, adaptive governance, 34-interview qualitative design, eight sub-camps, NVivo analysis, supplementary Sentinel-2 dates, land/wood/water access, coping and (mal)coping, institutional fragmentation, four-phase resource-governance transformation, limitations, research relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P018_2026_sobczak_szelc_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2026_sobczak_szelc_common_pool_resources_malcoping.pdf</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>The study is qualitative and male-dominated, covers a limited number of participants and sub-camps, and uses three Sentinel-2 images only as supplementary visual evidence. It provides no validated forest-loss quantity, fragmentation, carbon estimate or causal environmental effect. The Taylor &amp; Francis binary PDF was Cloudflare-blocked; the full text was reviewed from the open-access HTML version of record and a working archival PDF was saved to be replaced with the official publisher PDF later.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Begin Step 2.4S — P019 Rashid et al. (2021), vegetation and land-surface-temperature full-text review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>18 July 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Step 2.4S</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>P019 vegetation-loss and land-surface-temperature full-text review</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Verified the final 2021 journal record and reviewed the complete author-uploaded full text (RG personal copy); extracted Landsat dates, QGIS/SCP preprocessing, Random Forest (dzetsaka) classification, three LULC classes, OOB and Google Earth validation, post-classification transitions, gross (1,876.14 ha) and net (~836.46 ha) vegetation loss, Planck/NDVI-emissivity LST method, BMD comparison, class-specific thermal results, methodological limitations, internal inconsistencies, relevance and research gap.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>P019_2021_rashid_extraction_notes.docx; Literature_Review_Matrix.xlsx; Literature_Notes.docx; Research_Decision_Log.docx; 2021_rashid_vegetation_lst_rohingya_camps.pdf</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Broad vegetation class is not forest-specific; gross loss is sometimes described as forest loss; accuracy values differ across sections; maximum LST reported inconsistently (abstract ~34 °C vs table 35.7 °C); TIRS Bands 10 and 11 averaged; station air temperature is not direct LST validation; no causal design or propagated uncertainty. Springer subscription + RG login-gated binary; reviewed from author personal copy, working archival PDF saved to replace with the author/publisher PDF later.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Close Step 2.4 (all 19 papers reviewed: 16 full-text, 3 partial-access) and begin Step 2.5 — Cross-Paper Evidence Synthesis, Quality Appraisal and Gap Matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.5A</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Evidence family audit and non-independence control</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Built Evidence_Families (18 families) and Synthesis_Register (19 papers P001-P019) in the master matrix without altering existing sheets; classified independence, overlap (P011/P012), methodological (P007), partial-access (P003/P004/P015), comparative and qualitative evidence; added Decision 023.</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx (Evidence_Families, Synthesis_Register); Research_Decision_Log.docx (Decision 023)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 2.5B - Methodological Quality Appraisal (standardized quality scoring of all 19 papers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.5B</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Standardized methodological quality appraisal of all 19 papers</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Scored all reviewed papers across objective–design fit, data transparency, temporal adequacy, spatial/sample adequacy, measurement validity, validation and robustness, uncertainty handling and claim–method alignment. Normalized scores were calculated using applicable domains, while access status, direct relevance, causal status and independence were recorded separately.</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx (Quality_Rubric, Quality_Appraisal); Research_Decision_Log.docx (Decision 024)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Three papers remain partial-access and were capped at Moderate. Several studies are highly relevant but temporally limited, while some high-quality comparative or methodological papers are not direct Cox's Bazar outcome evidence.</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 2.5C — Cross-Paper Thematic Evidence Synthesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.5C1</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Core environmental-outcome thematic synthesis</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Synthesised forest and vegetation loss, fragmentation and connectivity, biomass and carbon, and restoration and resilience evidence using methodological quality, relevance and independence. Created an evidence-conflict register and separated forest from vegetation, gross from net loss, and greenness from carbon recovery.</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx (Thematic_Synthesis, Evidence_Conflicts); Research_Decision_Log.docx (Decision 025)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Numerical pooling is not appropriate because outcome definitions, spatial domains, observation periods and designs differ. Partial-access, proxy, comparative and overlapping evidence remains conditional or separately labelled.</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 2.5C2 — Causal, predictive, governance and conservation evidence synthesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.5C2</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Causal, predictive, governance and conservation evidence synthesis</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Synthesised causal attribution, prediction/LST/habitat risk, socioeconomic governance, and biodiversity/protected-area/elephant-corridor evidence. Added conflict controls separating causal estimates, scenarios, interventions, habitat-quality indices and corridor overlap.</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx (Thematic_Synthesis T05-T08, Evidence_Conflicts C06-C10); Research_Decision_Log.docx (Decision 026)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Causal effect sizes and scenarios remain non-combinable; intervention and corridor evidence is mechanism/prioritisation evidence rather than direct causal proof.</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 2.5D — Research Gap and Novelty Matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.5D</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Research gap and evidence-bounded novelty matrix</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Mapped twelve research gaps against the reviewed literature, identified the strongest existing evidence and methodological limitations, linked proposed contributions to current data feasibility, and separated locked, conditional and supporting contributions. Created a novelty-claims register containing allowed wording, prohibited wording and conditions for final use.</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx (Research_Gap_Matrix, Novelty_Claims_Register); Research_Decision_Log.docx (Decision 027)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Several contributions remain conditional on annual exposure reconstruction, covariate collection, SDID diagnostics, carbon calculations, uncertainty propagation, predictive validation and verified conservation layers.</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 2.5E — Final Literature Synthesis and Research Design Lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.5E</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Final literature synthesis and research-design lock</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Finalised six synthesis sections and provisionally locked the working title, aim, six objectives, six research questions, primary datasets, analytical roles, evidence-bounded novelty and conditional items. Locked measurement, causal attribution, prediction, mechanism and conservation roles separately.</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Literature_Review_Matrix.xlsx (Final_Literature_Synthesis, Research_Design_Lock); Research_Decision_Log.docx (Decision 028)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>The 2001-2025 framework is retained, but Hansen GFC v1.12 is confirmed through 2024 only; annual 2025 outcome remains conditional. Camp footprints, covariates, donor refinement, uncertainty, SHAP and conservation layers require empirical refinement.</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 3.2 — Annual Forest Outcome Dataset Construction, while refining D04 donor covariates and treatment definitions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>19 July 2026</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Step 2.6</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Final literature QA, consistency audit and freeze</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Verified D01–D12 source datasets and RC01–RC05 research components, P003 partial-access status, P011/P012 suffixes, Hansen 2001–2024 confirmed / 2025 conditional wording, cautious donor language, carbon-method condition, decision/progress alignment, formula errors, duplicate IDs and unsupported claims. Final result: Literature Phase: Verified and Frozen.</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Research_Decision_Log.docx (Decision 029); Literature_Review_Matrix.xlsx; Dataset_Inventory.xlsx; Research_Progress_Log.xlsx</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>No critical inconsistency remained after the final audit. The literature phase can reopen only under Decision 029 conditions.</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Begin Step 3.2 — Empirical Dataset Construction: 2016–2017 camp-footprint reconstruction; 2018 official-boundary validation; RC04 donor covariate refinement; full Hansen 2001–2024 extraction; annual 1 km forest-outcome table; JRC TMF validation; fragmentation pilot.</t>
         </is>
       </c>
     </row>

--- a/00_Project_Management/Research_Progress_Log.xlsx
+++ b/00_Project_Management/Research_Progress_Log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -2220,6 +2220,384 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>21–23 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2A</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Official 2018, 2023, 2024 boundaries collected and standardised</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Collected official IOM NPM 2018 Majhee Blocks, ISCG 2023 A1 Camp Outlines, and ISCG 2024 A2/A3 products; retained raw files and standardised derived layers.</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>04_Data/02_Camp_Exposure/Raw/Official_Boundaries; Processed official layers</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Different coordinate reference systems and administrative hierarchies.</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Reprojected derived layers to EPSG:32646 and processed each hierarchy separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>23–25 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2A</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2018 Majhee Blocks dissolved into 38 sites</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Dissolved 1,766 IOM NPM Majhee Blocks by Site into 38 administrative site geometries; completed strict geometry validation.</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>04_Data/02_Camp_Exposure/Processed/camp_admin_extent_2018_ringclean_v2.gpkg</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Two duplicate-node errors after dissolve.</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Applied targeted PyQGIS ring cleaning; final output has 38 valid and 0 invalid features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>23–25 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2A</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2024 A2 and A3 camp-level extents compared</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Dissolved A2 and A3 by CampSSID and compared hierarchy coverage and symmetric difference.</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>camp_admin_extent_2024_from_A2.gpkg; camp_admin_extent_2024_from_A3.gpkg</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>A3 misses one camp and one A2 block coverage.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Selected A2 as primary 33-camp extent; retained A3 for supplementary validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>25 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2A</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>2023–2024 camp-wise area comparison</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Joined 33 CampSSID values between 2023 A1 and 2024 A2-derived layers; zero unmatched camps and 0.057033 ha total absolute area difference.</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>04_Data/02_Camp_Exposure/Processed/camp_area_comparison_2023_2024_final.gpkg</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Required hierarchy consistency check.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Recorded administrative boundary-product comparison only; no physical expansion claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>25 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2B</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Next task identified: annual camp-exposure reconstruction</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Superseded: 2018–2023 crosswalk was completed and validated under subsequent Step 3.2B tasks; boundary stage frozen.</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>camp_crosswalk_2018_2023_final.csv; Research_Decision_Log.docx (034–036)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Earlier pending note retained for audit trail only.</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Proceed to Step 3.3 — Annual Camp Exposure Reconstruction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>25 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2B</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Constructed 2018–2023 spatial identifier crosswalk</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Harmonised 2018 Site and 2023 CampSSID identifiers through verified dominant spatial-overlap matching; wrote the 38-row master crosswalk.</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>04_Data/02_Camp_Exposure/Metadata/camp_crosswalk_2018_2023_final.csv</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>2018 used Site whereas 2023 used CampSSID.</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Dominant overlap selected 37 unique primary matches; Shamlapur retained unmatched_no_overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>25 Jul 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Step 3.2B</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Evaluated crosswalk confidence</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Calculated primary-overlap confidence and preserved nearest-neighbour evidence for the one unmatched site.</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Classified crosswalk; Validation confidence/overlap/Shamlapur QA screenshots</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>One site had no overlap.</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>33 High, 4 Moderate, 0 Low; Shamlapur explicitly unmatched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Step 3.2B</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Boundary stage frozen after crosswalk QA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Locked verified 2018/2023/2024 official layers, 2018–2023 crosswalk, QA evidence, Decision 036 and report v05; no overwrite of validated boundary workflow.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Full_Research_Report_v05_Boundary_Stage_Frozen.docx; official_boundary_layer_verification.csv; Research_Decision_Log.docx (Decision 036)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>None — boundary-processing phase complete.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Begin Step 3.3 — Annual Camp Exposure Reconstruction (2016–2025 exposure timeline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>25 July 2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Step 3.3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Annual Camp Exposure Reconstruction</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Not started. Next major empirical step after frozen boundary stage.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Missing annual footprints for 2016–2017 and other unavailable years.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Reconstruct annual camp footprints using locked official anchors and frozen crosswalk; start with 2016 pre-influx satellite baseline.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/00_Project_Management/Research_Progress_Log.xlsx
+++ b/00_Project_Management/Research_Progress_Log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.28515625" customWidth="1" style="2" min="1" max="1"/>
@@ -2574,27 +2574,111 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Not started. Next major empirical step after frozen boundary stage.</t>
+          <t>Initiated: reconstruction AOI validated and 2016 pre-influx Landsat baseline composite exported; settlement classification still pending.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>reconstruction_aoi_2016_2024_2km_final.gpkg; L8_SR_2016_preinflux_windowB_composite_30m.tif; Full_Research_Report_v06_Annual_Exposure_Reconstruction.docx</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Missing annual footprints for 2016–2017 and other unavailable years.</t>
+          <t>No physical 2016 camp footprint yet; classification and accuracy assessment pending.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Reconstruct annual camp footprints using locked official anchors and frozen crosswalk; start with 2016 pre-influx satellite baseline.</t>
+          <t>Proceed to settlement training-data preparation and 2016 physical-footprint classification (Step 3.3.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Step 3.3.1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Created and validated 2 km reconstruction AOI</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Merged locked 2018/2023/2024 A2 official camp layers (104 features), dissolved to one multipart geometry, buffered 2,000 m in EPSG:32646; strict validity 1/0/0; area ≈ 189.372 km². Uploaded EE asset reconstruction_aoi_2016_2024_2km.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>04_Data/02_Camp_Exposure/Annual_Reconstruction/01_AOI/reconstruction_aoi_2016_2024_2km_final.gpkg; official_camp_snapshots_2018_2024_merged.gpkg; official_camp_snapshots_2018_2024_union.gpkg; reconstruction_aoi_2016_2024_2km_wgs84.zip</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>AOI is processing extent only — not treatment/spillover/donor zone.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Select 2016 seasonal window and export baseline composite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>27 July 2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Step 3.3.2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Selected 2016 window and exported 11-band composite</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Compared three Landsat 8 C2 T1 L2 windows; selected Nov 2015–Apr 2016 (42 scenes; mean cloud 16.96%; AOI valid-pixel coverage 99.738%). Exported median SR composite with 6 reflectance bands + NDVI/NDBI/MNDWI/BSI + valid count.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>04_Data/02_Camp_Exposure/Annual_Reconstruction/03_Annual_Composites/L8_SR_2016_preinflux_windowB_composite_30m.tif; GEE scripts 01_2016_Landsat_Window_Test; 02_2016_Landsat_Composite_Export; Research_Decision_Log.docx (037–039); Full_Research_Report_v06_Annual_Exposure_Reconstruction.docx</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Composite QA complete; classification pending</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Documented as 2016 pre-influx settlement/land-surface baseline — not a camp footprint.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Prepare training data and classify 2016 settlement / physical footprint.</t>
         </is>
       </c>
     </row>
